--- a/CVM/05_PAINEL_RESULTADOS.xlsx
+++ b/CVM/05_PAINEL_RESULTADOS.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3.435 comunicados entregues à CVM após o fechamento · 57 papéis da B3 · 2018 a 2026 · hora oficial do Protocolo de Entrega</t>
+          <t>10.218 comunicados entregues à CVM após o fechamento · 57 papéis da B3 · 2018 a 2026 · hora oficial do Protocolo de Entrega</t>
         </is>
       </c>
     </row>
@@ -613,22 +613,22 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>1.034</t>
+          <t>1.032</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.132</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>+16.5%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>3e-49  (praticamente nula)</t>
+          <t>1e-53  (praticamente nula)</t>
         </is>
       </c>
     </row>
@@ -640,22 +640,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.061</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1.239</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>+31.6%</t>
+          <t>+16.8%</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2e-55  (praticamente nula)</t>
+          <t>5e-62  (praticamente nula)</t>
         </is>
       </c>
     </row>
@@ -667,22 +667,22 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>0.080%</t>
+          <t>0.076%</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.203%</t>
+          <t>0.172%</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.12 ponto</t>
+          <t>+0.10 ponto</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>0.010%</t>
+          <t>0.011%</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>0.017%</t>
+          <t>0.006%</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>0.92  (pode ser sorte)</t>
+          <t>0.89  (pode ser sorte)</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>1.512</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>2.658</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr"/>
@@ -792,12 +792,12 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>1.304</t>
+          <t>4.219</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
@@ -811,12 +811,12 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>1.814</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -825,7 +825,7 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>RESPOSTA: NÃO. 52,3% não mexeram. O efeito médio vem de uma MINORIA de casos — é o efeito de cauda.</t>
+          <t>RESPOSTA: NAO. 59.2% nao mexeram. O efeito medio vem de uma MINORIA de casos -- e o efeito de cauda.</t>
         </is>
       </c>
     </row>
@@ -866,176 +866,298 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>O rótulo da CVM (Fato Relevante)</t>
+          <t>O rotulo da CVM</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>não se aplica</t>
+          <t>nao se aplica</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>IMPOSSÍVEL</t>
+          <t>IMPOSSIVEL</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>o rótulo não diz o lado</t>
+          <t>o rotulo nao diz o lado</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Nossa leitura — no salto da abertura</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>54.7%</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>57.4%</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>-2.7 pts</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>PERDE do palpite fixo</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Nossa leitura - em FATO RELEVANTE</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>54.3%</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>51.7%</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>+2.57 pts</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0.026  *</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Nossa leitura — no pregão inteiro</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>55.0%</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>50.2%</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>+4.9 pts</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>0.012</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>RESPOSTA: SÓ a nossa leitura pode responder isso — e ganha por 4,9 pontos de quem não lê nada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Nossa leitura - em Comunicado ao Mercado</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>50.8%</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>50.8%</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>+0.00 pts</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>0.552  (pode ser sorte)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Nossa leitura - os dois juntos</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>51.9%</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>51.1%</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>+0.82 pts</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>0.076  (pode ser sorte)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>RESPOSTA: so a nossa leitura pode responder -- e SO funciona no Fato Relevante, onde ganha 2,6 pontos. No Comunicado, ganha zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>A LEI ACERTA? Fato Relevante contra Comunicado ao Mercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Regua</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Fato Relevante</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Comunicado</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Quantas vezes mais</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Chance de ser sorte</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Sacolejo do preco</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>+18.1%</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+6.1%</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>3.0x</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>1e-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>VOLUME negociado</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>+36.3%</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+11.1%</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>3.3x</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>6e-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>SIM. O que a lei chama de RELEVANTE mexe 3 VEZES MAIS que o que ela chama de simples comunicado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>E ONDE ESTÁ O SINAL?</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>O programa disse que era...</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Casos</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>O preço fez, em média</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Positivo</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>+0.014%  nada</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+0.177%  </t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr"/>
+      <c r="E40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Neutro</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>2.939</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>+0.028%  nada</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr"/>
-      <c r="E33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>8.026</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>+0.009%  nada</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr"/>
+      <c r="E41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>NEGATIVO</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-0.353%  </t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr"/>
-      <c r="E34" s="12" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>1.310</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-0.138%  </t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr"/>
+      <c r="E42" s="12" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>O programa reconhece a notícia RUIM. Não reconhece a BOA.</t>
         </is>
@@ -1233,7 +1355,7 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    sem notícia: 1.034 no sacolejo, 1.065 no volume</t>
+          <t xml:space="preserve">    sem notícia: 1.032 no sacolejo, 1.061 no volume</t>
         </is>
       </c>
     </row>
@@ -1350,41 +1472,41 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>780</v>
+        <v>2192</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0034</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>+0.123</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>+0.132</t>
+          <t>+0.095</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr"/>
@@ -1396,41 +1518,41 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>636</v>
+        <v>1415</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>0.0192</t>
+          <t>0.0003</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>0.546</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>+0.103</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>+0.128</t>
+          <t>+0.105</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr"/>
@@ -1442,41 +1564,41 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>780</v>
+        <v>2192</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>+3.21</t>
+          <t>+0.82</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>0.0762</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>0.513</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>+0.091</t>
+          <t>+0.034</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>+0.092</t>
+          <t>+0.035</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr"/>
@@ -1488,41 +1610,41 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>636</v>
+        <v>1415</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>+4.87</t>
+          <t>+0.07</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>0.0124</t>
+          <t>0.5950</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>0.507</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>+0.100</t>
+          <t>+0.015</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>+0.102</t>
+          <t>+0.015</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr"/>
@@ -1628,19 +1750,19 @@
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>0.0528</v>
+        <v>0.0359</v>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0003</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>0.0553</v>
+        <v>0.0253</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>0.0105</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr"/>
@@ -1656,19 +1778,19 @@
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>0.0296</v>
+        <v>0.0199</v>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>0.0708</t>
+          <t>0.0440</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>0.0401</v>
+        <v>0.007</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>0.0146</t>
+          <t>0.4782</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr"/>
@@ -1762,76 +1884,76 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>2024-10-18 18:59</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>HYPE3</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Aquisição de Ações de Emissão da Própria Companhia||Modificação de Projeções Divulgadas</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>2024-10-21</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>9.1x</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>8.7x</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>+1.9%</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2024-11-08 18:45</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>OIBR3</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Cumprimento das Condicionantes Anatel para Aumento de Capital</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>10.2x</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>5.6x</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>-50.0%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-01-15 20:51</t>
+          <t>2019-08-14 23:45</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CVCB3</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Plano de sucessão da Companhia</t>
+          <t>Apresentação 2T19</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2019-08-15</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>5.4x</t>
+          <t>8.1x</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>5.0x</t>
+          <t>7.3x</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1841,81 +1963,81 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>2025-09-30 23:08</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>OIBR3</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Decisão Judicial - Suspensão de Obrigações e Afastamento da Gestão</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>5.1x</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>15.1x</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>-28.1%</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>2024-09-04 20:05</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>LIGT3</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Nova Data da Assembleia do Scheme of Arrangement</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>6.8x</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>10.9x</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>+18.8%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2025-11-07 19:31</t>
+          <t>2019-07-01 20:01</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>OIBR3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Manifestação sobre a Continuidade do Grupo Oi</t>
+          <t>Vale informa datas de divulgação do desempenho do segundo trimestre de 2019</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2019-07-02</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>4.9x</t>
+          <t>6.2x</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>5.7x</t>
+          <t>4.0x</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -1925,81 +2047,81 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>2024-06-28 18:07</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>SLCE3</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Avaliação de Terras 2024</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>4.9x</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>2.9x</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>+7.0%</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-15 20:51</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>CVCB3</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Plano de sucessão da Companhia</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>5.4x</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>5.0x</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>-11.4%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2018-03-14 19:08</t>
+          <t>2023-02-28 21:49</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>NTCO3</t>
+          <t>HAPV3</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Modificação de Projeções Divulgadas</t>
+          <t>Versões português e inglês</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2018-03-15</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>4.3x</t>
+          <t>5.2x</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3.5x</t>
+          <t>12.7x</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -2009,39 +2131,39 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-39.7%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06 18:32</t>
+          <t>2025-09-30 23:08</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>LREN3</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Projeções</t>
+          <t>Decisão Judicial - Suspensão de Obrigações e Afastamento da Gestão</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>4.1x</t>
+          <t>5.1x</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>10.4x</t>
+          <t>15.1x</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -2051,165 +2173,165 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-28.1%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>2025-01-09 18:24</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-07 19:31</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>OIBR3</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Conclusa~o das Negociac¸o~es para alienação da UPI Ativos TV por Assinatura</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>4.1x</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>7.9x</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Manifestação sobre a Continuidade do Grupo Oi</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>4.9x</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>5.7x</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>-44.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>2024-06-28 18:07</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Avaliação de Terras 2024</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>4.9x</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>2.9x</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>+6.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>2025-11-13 18:18</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>HAPV3</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Programa de Recompra de Ações</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>4.0x</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>10.1x</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>-6.0%</t>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>+7.0%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>2022-02-23 18:42</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>RDOR3</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Associação Rede D'Or e SulAmérica</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>2022-02-24</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>4.0x</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>5.8x</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>-8.0%</t>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>2025-03-13 18:30</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>B3SA3</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Destaques Operacionais - Fevereiro de 2025</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>4.6x</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>+10.4%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2024-05-08 18:37</t>
+          <t>2018-03-14 19:08</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>COGN3</t>
+          <t>NTCO3</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Revisão do guidance da Controlada Vasta - Alteração no ACV (Valor Anual do Contrato) de  16% - 18% para 12% no ciclo 2024</t>
+          <t>Modificação de Projeções Divulgadas</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2018-03-15</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>3.9x</t>
+          <t>4.3x</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>5.2x</t>
+          <t>3.5x</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -2219,39 +2341,39 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2022-06-29 17:43</t>
+          <t>2019-08-15 18:44</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LIGT3</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Renúncia de Administrador</t>
+          <t>Apresentação 2T19</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>3.9x</t>
+          <t>4.3x</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>6.7x</t>
+          <t>7.2x</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -2261,81 +2383,81 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>2023-11-13 22:13</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>CSNA3</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Alteração de Projeções</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>3.9x</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>4.7x</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>+8.3%</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06 18:32</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>LREN3</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Projeções</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>4.1x</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>10.4x</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>-8.4%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2024-11-05 19:01</t>
+          <t>2025-01-09 18:24</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>GOAU4</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Cancelamento de ações em tesouraria</t>
+          <t>Conclusa~o das Negociac¸o~es para alienação da UPI Ativos TV por Assinatura</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>3.9x</t>
+          <t>4.1x</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>3.8x</t>
+          <t>7.9x</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -2345,165 +2467,165 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>+8.8%</t>
+          <t>+6.3%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>2025-08-04 19:35</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>BBSE3</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Modificação de Projeções Divulgadas</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>3.8x</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>1.3x</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>+1.1%</t>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2023-11-08 19:49</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>BRAV3</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Dados de Produção - Outubro 2023</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>4.1x</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>4.3x</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>-3.9%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>2020-03-10 22:00</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>OIBR3</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Proposta pela Móvel</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>3.8x</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>3.9x</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>+4.4%</t>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-13 18:18</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>HAPV3</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Programa de Recompra de Ações</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>4.0x</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>10.1x</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>-6.0%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>2021-04-16 18:28</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Petrobras sobre renúncia de Conselheiro de Administração</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>2021-04-19</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>3.7x</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>+5.6%</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>2024-11-13 18:50</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>LIGT3</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Ratificação das versões finais dos Instrumentos Locais</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>4.0x</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>6.3x</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>-6.3%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06 17:52</t>
+          <t>2024-03-06 22:45</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ASAI3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Eleição do Sr. Rafael Sachete da Silva para o cargo de Diretor de Relações com Investidores</t>
+          <t>Release de ESG 4T23 e 2023</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>3.7x</t>
+          <t>4.0x</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>2.6x</t>
+          <t>3.2x</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -2513,39 +2635,39 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2019-11-07 21:47</t>
+          <t>2022-02-23 18:42</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>CVCB3</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Renuncia DRI</t>
+          <t>Associação Rede D'Or e SulAmérica</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>2019-11-08</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>3.7x</t>
+          <t>4.0x</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>11.0x</t>
+          <t>5.8x</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -2555,39 +2677,39 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-8.0%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2025-12-16 23:52</t>
+          <t>2024-08-14 20:06</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>BRAV3</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Esclarecimento acerca de notícia divulgada na mídia</t>
+          <t>Apresentação de Resultados 2T24</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>3.6x</t>
+          <t>3.9x</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>3.7x</t>
+          <t>8.6x</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -2597,81 +2719,81 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>+3.6%</t>
+          <t>+10.2%</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2018-09-24 19:40</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>BRKM5</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Celebração, Alteração ou Rescisão de Acordo de Acionistas</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>2018-09-25</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>3.6x</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>1.2x</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>+4.0%</t>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>2024-05-08 18:37</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>COGN3</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Revisão do guidance da Controlada Vasta - Alteração no ACV (Valor Anual do Contrato) de  16% - 18% para 12% no ciclo 2024</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>3.9x</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>5.2x</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>-5.8%</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2020-03-11 17:32</t>
+          <t>2022-06-29 17:43</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>BRKM5</t>
+          <t>LIGT3</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Término da monitoria na Braskem prevista no Acordo de Leniência firmado entre a Companhia e Ministério Público Federal em 14 de dezembro de 2016</t>
+          <t>Renúncia de Administrador</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>2020-03-12</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>3.6x</t>
+          <t>3.9x</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>2.0x</t>
+          <t>6.7x</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -2681,81 +2803,81 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-17.0%</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>2020-04-23 20:35</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>SBSP3</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Rerratificação dos termos e condições da 25ª  emissão de debêntures</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>2020-04-24</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>3.6x</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>2.2x</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>-11.5%</t>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2024-11-05 19:01</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>GOAU4</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Cancelamento de ações em tesouraria</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>3.9x</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>+8.8%</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2022-11-09 23:53</t>
+          <t>2018-11-07 19:49</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>B3SA3</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Aquisição da Neurotech</t>
+          <t>Apresentação de Resultados 3T18</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2018-11-08</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>3.5x</t>
+          <t>3.8x</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>2.7x</t>
+          <t>4.5x</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -2765,207 +2887,207 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-8.8%</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2024-09-26 21:28</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>SLCE3</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Guidance safra 2024/25</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>2.5x</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>2024-11-06 21:45</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>OIBR3</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação de Resultados 3T24</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>1.9x</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2025-08-04 19:35</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>BBSE3</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Modificação de Projeções Divulgadas</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>1.3x</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>+5.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>2024-05-08 18:29</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>BBAS3</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Remuneração Complementar aos Acionistas 1T24</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>3.4x</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>4.2x</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>+1.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2020-03-10 22:00</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>OIBR3</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Proposta pela Móvel</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>3.9x</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>+4.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>2024-03-08 20:16</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras esclarece notícia divulgada na mídia</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3.6x</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>CAIU</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>-4.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>2025-11-14 18:41</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>RAIL3</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Alterações composição conselho de administração e comitês de assessoramento</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>3.4x</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>1.8x</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>-9.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>2018-12-28 19:55</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>SBSP3</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Renúncia da Diretora Presidente</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>2019-01-02</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>3.4x</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>3.9x</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>+8.7%</t>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>-2.9%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2019-10-03 21:55</t>
+          <t>2021-04-16 18:28</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>RADL3</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Divulgação de Projeções</t>
+          <t>Petrobras sobre renúncia de Conselheiro de Administração</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2019-10-04</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>3.3x</t>
+          <t>3.7x</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>3.2x</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -2975,39 +3097,39 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>+6.0%</t>
+          <t>+5.6%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11 22:43</t>
+          <t>2026-08-06 17:52</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>ASAI3</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Alteracao e inclusao de projecao</t>
+          <t>Eleição do Sr. Rafael Sachete da Silva para o cargo de Diretor de Relações com Investidores</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>3.3x</t>
+          <t>3.7x</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3.6x</t>
+          <t>2.6x</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -3017,39 +3139,39 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-3.0%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2018-02-22 18:54</t>
+          <t>2024-02-27 19:36</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>CCRO3</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Apresentação 4T17</t>
+          <t>Apresentação dos Resultados do 4T23</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2018-02-23</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>3.3x</t>
+          <t>3.7x</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>4.9x</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -3059,39 +3181,39 @@
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+5.8%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2018-09-11 18:33</t>
+          <t>2025-05-08 22:33</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Aumento de Capital</t>
+          <t>Release ESG 1T25</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>3.3x</t>
+          <t>3.6x</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>4.3x</t>
+          <t>3.1x</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -3101,123 +3223,123 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-10.4%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>2023-03-02 21:47</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>OIBR3</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Novo material de blow out das discussões com credores</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>3.3x</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>2.6x</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>-17.9%</t>
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2025-12-16 23:52</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>BRAV3</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Esclarecimento acerca de notícia divulgada na mídia</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>3.6x</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>3.7x</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>+3.6%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>2025-04-29 18:50</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>CPFE3</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Cisão parcial da CPFL Geração,  com a incorporação do acervo cindido pela  CPFL Energia</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>1.6x</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>-2.3%</t>
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>2018-09-24 19:40</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>BRKM5</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Celebração, Alteração ou Rescisão de Acordo de Acionistas</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>2018-09-25</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>3.6x</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>1.2x</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2022-11-08 19:06</t>
+          <t>2018-04-25 23:00</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Apresentação de Resultados 1T18</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>3.2x</t>
+          <t>3.6x</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>10.7x</t>
+          <t>3.9x</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -3227,81 +3349,81 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>2025-07-01 23:33</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>OIBR3</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Aditamento ao Plano de Recuperação Judicial Oi</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>3.1x</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>-9.7%</t>
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>2025-03-21 18:46</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>BRAV3</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Apresentação Divulgação de Resultados 4T24 &amp;amp 2024</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>3.6x</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>2.6x</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>+9.7%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2025-03-19 19:51</t>
+          <t>2020-03-11 17:32</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>HAPV3</t>
+          <t>BRKM5</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Demonstrações Financeiras e Acordo SUS/ANS</t>
+          <t>Término da monitoria na Braskem prevista no Acordo de Leniência firmado entre a Companhia e Ministério Público Federal em 14 de dezembro de 2016</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>3.2x</t>
+          <t>3.6x</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>5.7x</t>
+          <t>2.0x</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -3311,39 +3433,39 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-27.6%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2024-10-23 21:47</t>
+          <t>2020-04-23 20:35</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>BRKM5</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Relatório de Produção e Vendas 3T24</t>
+          <t>Rerratificação dos termos e condições da 25ª  emissão de debêntures</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2020-04-24</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>3.2x</t>
+          <t>3.6x</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>1.7x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -3353,91 +3475,91 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-11.5%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-10 18:40</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>EGIE3</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Oferta Pública de Distribuição de Ações</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>3.0x</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>2022-11-09 23:53</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>B3SA3</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Aquisição da Neurotech</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>2.7x</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>-13.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>2021-11-19 20:28</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>TIMS3</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Próximas Lives Programadas.</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>2021-11-22</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>3.5x</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>5.1x</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>+3.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>2025-02-19 19:00</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>GOAU4</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Plano de Investimentos - CAPEX 2025</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>2025-02-20</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>2.3x</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>-5.0%</t>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>+1.7%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3601,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>397 comunicados da Petrobras após o fechamento no período</t>
+          <t>1273 comunicados da Petrobras após o fechamento no período</t>
         </is>
       </c>
     </row>
@@ -3526,51 +3648,51 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>2021-04-16 18:28</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2024-03-08 20:16</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Petrobras sobre renúncia de Conselheiro de Administração</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>2021-04-19</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>3.7x</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>3.2x</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>+5.6%</t>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras esclarece notícia divulgada na mídia</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>3.6x</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>-2.9%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2019-05-07 18:55</t>
+          <t>2021-04-16 18:28</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -3580,22 +3702,22 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Petrobras aprova pagamento de remuneração aos acionistas</t>
+          <t>Petrobras sobre renúncia de Conselheiro de Administração</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2019-05-08</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>3.1x</t>
+          <t>3.7x</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>2.1x</t>
+          <t>3.2x</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -3605,14 +3727,14 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+5.6%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2024-04-03 20:41</t>
+          <t>2020-03-06 18:35</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3622,22 +3744,22 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Petrobras informa sobre indicações por minoritários para o Conselho de Administração e para o Conselho Fiscal</t>
+          <t>Petrobras inicia fase vinculante de ativos de E&amp;ampP</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>2.9x</t>
+          <t>3.3x</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>5.7x</t>
+          <t>3.5x</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -3647,56 +3769,56 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-35.2%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>2023-02-27 21:21</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>2019-05-07 18:55</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Candidatos indicados pelo acionista controlador para o Conselho Fiscal</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>2023-02-28</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>2.8x</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>2.3x</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>-3.5%</t>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras aprova pagamento de remuneração aos acionistas</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>2019-05-08</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>3.1x</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>2.1x</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>+3.8%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2025-11-27 21:44</t>
+          <t>2022-06-15 20:02</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -3706,123 +3828,123 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Petrobras aprova Plano de Negócios 2026-2030</t>
+          <t>Petrobras sobre venda da LUBNOR</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
+          <t>2.9x</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>2.9x</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>-6.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2024-04-03 20:41</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras informa sobre indicações por minoritários para o Conselho de Administração e para o Conselho Fiscal</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>2.9x</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>5.7x</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>2019-11-05 19:44</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras esclarece sobre o TCC para o mercado de gás</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
           <t>2.8x</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>1.7x</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>-1.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>2023-01-03 20:45</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Petrobras sobre ofício do Ministério das Minas e Energia</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>2023-01-04</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>2.8x</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>2.4x</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>2.1x</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>+3.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>2024-03-07 22:06</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Petrobras sobre remuneração aos acionistas</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>2024-03-08</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>2.5x</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>6.0x</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>-9.6%</t>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>+0.2%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2025-02-26 20:10</t>
+          <t>2023-02-27 21:21</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -3832,165 +3954,165 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Petrobras informa sobre remuneração aos acionistas</t>
+          <t>Candidatos indicados pelo acionista controlador para o Conselho Fiscal</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
+          <t>2.8x</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>2.3x</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>-3.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-27 21:44</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras aprova Plano de Negócios 2026-2030</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>2.8x</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>1.7x</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-1.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>2023-01-03 20:45</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras sobre ofício do Ministério das Minas e Energia</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>2023-01-04</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>2.8x</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
           <t>2.4x</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>4.3x</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>-3.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>2025-11-06 19:20</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>+3.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>2022-06-17 21:45</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Petrobras informa sobre remuneração aos acionistas</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>2.4x</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras sobre candidatos indicados por acionistas minoritários para o Conselho de Administração</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>2.7x</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>1.4x</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>+3.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>2019-07-25 19:47</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Petrobras informa sobre o exercício da opção de lote suplementar no âmbito da oferta pública de ações da Petrobras Distribuidora S.A.</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>2019-07-26</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>2.3x</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>2.8x</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>-2.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>2023-07-26 18:43</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Relatório de Produção e Vendas 2T23</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>2.3x</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>1.9x</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>-5.3%</t>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>+1.1%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2019-07-24 18:05</t>
+          <t>2024-06-06 18:30</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4000,22 +4122,22 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Petrobras assina contratos para venda de ativos em águas rasas somando US$ 1,5 bilhão</t>
+          <t>Petrobras aprova reativação da fábrica de fertilizantes de Araucária (PR)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>2.7x</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>1.0x</t>
+          <t>1.3x</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -4025,140 +4147,140 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-06 19:19</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>2025-06-02 18:54</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Petrobras informa sobre remuneração aos acionistas</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>2.2x</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>3.6x</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>-3.0%</t>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras informa sobre perspectiva de rating global pela Moody's</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>2.6x</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>2.0x</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>2020-08-25 19:36</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>2023-01-16 20:09</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Petrobras sobre Revolving Credit Lines</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>2.0x</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>1.4x</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>-2.9%</t>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras sobre acordo de leniência</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>2023-01-17</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>2.4x</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>1.8x</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>+6.0%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>2021-02-19 21:01</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>2025-02-13 20:38</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Petrobras sobre ofício do Ministério das Minas e Energia</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>2021-02-22</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>2.0x</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>7.6x</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>-23.2%</t>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras informa sobre atualização monetária da remuneração aos acionistas relativa ao 3T24</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>2.4x</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>1.8x</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>+3.0%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2022-04-06 20:42</t>
+          <t>2021-12-01 19:04</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -4168,22 +4290,22 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Petrobras sobre ofício do Ministério das Minas e Energia</t>
+          <t>Petrobras sobre certificação de Governança</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
+          <t>2021-12-02</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>2.0x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>1.8x</t>
+          <t>1.9x</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -4193,14 +4315,14 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>+5.1%</t>
+          <t>+7.4%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2022-11-03 19:04</t>
+          <t>2020-03-11 20:43</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -4210,22 +4332,22 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Petrobras sobre remuneração aos acionistas</t>
+          <t>Petrobras sobre recorde de produção em Búzios</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>2.0x</t>
+          <t>2.4x</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>1.3x</t>
+          <t>1.1x</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -4235,56 +4357,56 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-22.9%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>2019-10-23 18:03</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>2025-11-06 19:20</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Petrobras sobre Aditivo ao Contrato de Cessão Onerosa</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>2019-10-24</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>2.0x</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>1.5x</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>-2.2%</t>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras informa sobre remuneração aos acionistas</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>2.4x</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>2.7x</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>+3.7%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2023-06-07 20:09</t>
+          <t>2020-06-12 18:29</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -4294,207 +4416,207 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Petrobras sobre Polo Potiguar</t>
+          <t>Petrobras inicia fase vinculante de usinas eólicas</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>2.0x</t>
+          <t>2.3x</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
+          <t>1.0x</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2021-10-18 21:37</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras esclarece sobre notícias da imprensa</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>2021-10-19</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>2.3x</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
           <t>1.5x</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>-5.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2020-03-09 18:10</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras assina contrato para venda de campos terrestres</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>2020-03-10</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>2.3x</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>2.1x</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>+4.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2018-12-28 20:12</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>+9.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2019-08-20 17:25</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Pedido de Registro de Oferta Pública de Debêntures</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>2019-01-02</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras informa sobre decisão favorável do CARF relacionada à cobrança de CIDE-Importação referente a contratos de afretamento</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>2019-08-21</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>2.3x</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>1.7x</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>+5.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>2023-07-26 18:43</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Relatório de Produção e Vendas 2T23</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>2.3x</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>1.9x</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>0.9x</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>+5.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>2019-02-27 20:43</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Petrobras aprova pagamento de dividendos</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>2019-02-28</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>1.9x</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>1.9x</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>CAIU</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>2019-11-01 18:40</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Petrobras divulga teaser de E&amp;ampP na Bacia de Sergipe-Alagoas</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>2019-11-04</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>1.9x</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>1.4x</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2018-12-21 20:16</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Eleição do novo Presidente da Petrobras e mudanças na Administração</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>2018-12-26</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>1.9x</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>0.8x</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>+4.0%</t>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>-5.3%</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2024-06-11 19:25</t>
+          <t>2022-10-21 18:50</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -4504,22 +4626,22 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Atualização do valor por ação de dividendos e JCP do 1T24</t>
+          <t>Petrobras sobre venda da rede de fibra óptica onshore</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>1.8x</t>
+          <t>2.3x</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>1.7x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -4529,98 +4651,98 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2020-11-06 18:35</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>2019-03-21 18:18</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Petrobras conclui a venda do campo de Baúna</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>2020-11-09</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>1.8x</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>2.5x</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>+9.0%</t>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Hibernação da fábrica de fertilizantes na Bahia</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>2019-03-22</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>2.2x</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>1.6x</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>-5.6%</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>2021-01-26 18:03</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06 19:19</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Petrobras sobre Reservas Provadas em 2020</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>2021-01-27</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>1.8x</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>1.2x</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>+1.5%</t>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras informa sobre remuneração aos acionistas</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>2.2x</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3.6x</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>-3.0%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2022-07-28 19:49</t>
+          <t>2020-07-13 20:17</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -4630,22 +4752,22 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Petrobras sobre remuneração aos acionistas</t>
+          <t>Petrobras sobre venda de asfalto pela Reduc</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2022-07-29</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>1.8x</t>
+          <t>2.1x</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>1.7x</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -4655,56 +4777,56 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+3.3%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>2019-05-17 21:59</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>2019-07-15 19:53</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Petrobras informa sobre decisão de primeira instância na ação anulatória da sentença arbitral do caso Vantage nos EUA</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>2019-05-20</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>1.8x</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras divulga início de fase não vinculante para venda de ativos em refino e logística no país</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>2.1x</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>1.4x</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>+3.3%</t>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>-1.2%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2022-07-05 18:43</t>
+          <t>2022-12-13 20:23</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -4714,22 +4836,22 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Petrobras sobre venda de sua participação na Deten</t>
+          <t>Petrobras sobre o Polo Bahia Terra</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-12-14</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>1.8x</t>
+          <t>2.1x</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>1.1x</t>
+          <t>4.4x</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -4739,14 +4861,14 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-8.3%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2021-07-05 22:43</t>
+          <t>2025-04-03 19:43</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -4756,22 +4878,22 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Petrobras assina contrato para venda de ativos de E&amp;ampP em Alagoas</t>
+          <t>Petrobras arquiva Form 20-F 2024</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>1.8x</t>
+          <t>2.1x</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>1.9x</t>
+          <t>3.9x</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -4781,7 +4903,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.1%</t>
         </is>
       </c>
     </row>

--- a/CVM/05_PAINEL_RESULTADOS.xlsx
+++ b/CVM/05_PAINEL_RESULTADOS.xlsx
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10.218 comunicados entregues à CVM após o fechamento · 57 papéis da B3 · 2018 a 2026 · hora oficial do Protocolo de Entrega</t>
+          <t>11.161 comunicados entregues à CVM após o fechamento · 57 papéis da B3 · 2018 a 2026 · hora oficial do Protocolo de Entrega</t>
         </is>
       </c>
     </row>
@@ -613,22 +613,22 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1.031</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>1.130</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>+9.8%</t>
+          <t>+9.6%</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1e-53  (praticamente nula)</t>
+          <t>7e-55  (praticamente nula)</t>
         </is>
       </c>
     </row>
@@ -640,22 +640,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1.060</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>+16.8%</t>
+          <t>+16.5%</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>5e-62  (praticamente nula)</t>
+          <t>4e-62  (praticamente nula)</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>0.076%</t>
+          <t>0.077%</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.172%</t>
+          <t>0.161%</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.10 ponto</t>
+          <t>+0.08 ponto</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>0.011%</t>
+          <t>0.012%</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>0.006%</t>
+          <t>-0.001%</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>0.89  (pode ser sorte)</t>
+          <t>0.74  (pode ser sorte)</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>1.642</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>2.658</t>
+          <t>2.900</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>4.219</t>
+          <t>4.599</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>1.814</t>
+          <t>1.991</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>RESPOSTA: NAO. 59.2% nao mexeram. O efeito medio vem de uma MINORIA de casos -- e o efeito de cauda.</t>
+          <t>RESPOSTA: NAO. 59.3% nao mexeram. O efeito medio vem de uma MINORIA de casos -- e o efeito de cauda.</t>
         </is>
       </c>
     </row>
@@ -925,22 +925,22 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>+0.00 pts</t>
+          <t>+0.43 pts</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>0.552  (pode ser sorte)</t>
+          <t>0.443  (pode ser sorte)</t>
         </is>
       </c>
     </row>
@@ -952,22 +952,22 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>+0.82 pts</t>
+          <t>+1.07 pts</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>0.076  (pode ser sorte)</t>
+          <t>0.060  (pode ser sorte)</t>
         </is>
       </c>
     </row>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>+18.1%</t>
+          <t>+18.2%</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>+6.1%</t>
+          <t>+6.9%</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>3.0x</t>
+          <t>2.6x</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>1e-19</t>
+          <t>7e-18</t>
         </is>
       </c>
     </row>
@@ -1047,22 +1047,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>+36.3%</t>
+          <t>+36.4%</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+11.1%</t>
+          <t>+12.2%</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>3.3x</t>
+          <t>3.0x</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>6e-28</t>
+          <t>5e-26</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>967</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">+0.177%  </t>
+          <t xml:space="preserve">+0.174%  </t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr"/>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>8.026</t>
+          <t>8.825</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>+0.009%  nada</t>
+          <t>-0.010%  nada</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr"/>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>1.310</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.138%  </t>
+          <t xml:space="preserve">-0.136%  </t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    sem notícia: 1.032 no sacolejo, 1.061 no volume</t>
+          <t xml:space="preserve">    sem notícia: 1.031 no sacolejo, 1.060 no volume</t>
         </is>
       </c>
     </row>
@@ -1472,41 +1472,41 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2192</v>
+        <v>2336</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>0.0034</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>+0.089</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>+0.095</t>
+          <t>+0.094</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1415</v>
+        <v>1508</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0002</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>+0.103</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>+0.105</t>
+          <t>+0.102</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr"/>
@@ -1564,41 +1564,41 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>2192</v>
+        <v>2336</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>+0.82</t>
+          <t>+1.07</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>0.0762</t>
+          <t>0.0597</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>0.515</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>+0.034</t>
+          <t>+0.036</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>+0.035</t>
+          <t>+0.037</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr"/>
@@ -1610,41 +1610,41 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1415</v>
+        <v>1508</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
+          <t>50.9%</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
           <t>50.7%</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>50.7%</t>
-        </is>
-      </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>+0.07</t>
+          <t>+0.13</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>0.5950</t>
+          <t>0.5197</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>0.509</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>+0.015</t>
+          <t>+0.018</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>+0.015</t>
+          <t>+0.018</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>0.0359</v>
+        <v>0.0345</v>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
@@ -1758,11 +1758,11 @@
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>0.0253</v>
+        <v>0.0234</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>0.0105</t>
+          <t>0.0134</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr"/>
@@ -1778,19 +1778,19 @@
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>0.0199</v>
+        <v>0.0187</v>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>0.0440</t>
+          <t>0.0487</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>0.007</v>
+        <v>0.0071</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>0.4782</t>
+          <t>0.4510</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr"/>
@@ -1886,32 +1886,32 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2024-11-08 18:45</t>
+          <t>2025-11-12 19:57</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>OIBR3</t>
+          <t>HAPV3</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Cumprimento das Condicionantes Anatel para Aumento de Capital</t>
+          <t>Apresentação de Resultados 3T25 - Português e Inglês</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>10.2x</t>
+          <t>10.4x</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>5.6x</t>
+          <t>25.1x</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1921,207 +1921,207 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-54.8%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>2024-11-08 18:45</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>OIBR3</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Cumprimento das Condicionantes Anatel para Aumento de Capital</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>10.2x</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>5.6x</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
           <t>2019-08-14 23:45</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>OIBR3</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Apresentação 2T19</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>2019-08-15</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>8.1x</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>7.3x</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>CAIU</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>-19.8%</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-18 21:38</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>HAPV3</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Apresentação de Resultados 4T25 - Português e Inglês</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>7.0x</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>5.2x</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>+14.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>2024-09-04 20:05</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>LIGT3</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Nova Data da Assembleia do Scheme of Arrangement</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>6.8x</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>10.9x</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>+18.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>2019-07-01 20:01</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>VALE3</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Vale informa datas de divulgação do desempenho do segundo trimestre de 2019</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>2019-07-02</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>6.2x</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>4.0x</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>-4.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>2026-01-15 20:51</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>CVCB3</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Plano de sucessão da Companhia</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>5.4x</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>5.0x</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>-11.4%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2023-02-28 21:49</t>
+          <t>2019-07-01 20:01</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>HAPV3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Versões português e inglês</t>
+          <t>Vale informa datas de divulgação do desempenho do segundo trimestre de 2019</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2019-07-02</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>5.2x</t>
+          <t>6.2x</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>12.7x</t>
+          <t>4.0x</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -2131,39 +2131,39 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>-39.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2025-09-30 23:08</t>
+          <t>2026-01-15 20:51</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>OIBR3</t>
+          <t>CVCB3</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Decisão Judicial - Suspensão de Obrigações e Afastamento da Gestão</t>
+          <t>Plano de sucessão da Companhia</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>5.1x</t>
+          <t>5.4x</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>15.1x</t>
+          <t>5.0x</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -2173,249 +2173,249 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-11.4%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>2023-02-28 21:49</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>HAPV3</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Versões português e inglês</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>5.2x</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>12.7x</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>-39.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-12 20:08</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>HAPV3</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação 2T26</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>5.0x</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>8.8x</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-40.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
           <t>2025-11-07 19:31</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>OIBR3</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Manifestação sobre a Continuidade do Grupo Oi</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>4.9x</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>5.7x</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>CAIU</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>-44.2%</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>2024-06-28 18:07</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>SLCE3</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Avaliação de Terras 2024</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>4.9x</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>2.9x</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>+7.0%</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>2025-03-13 18:30</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>B3SA3</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Destaques Operacionais - Fevereiro de 2025</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>4.6x</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>3.5x</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>+10.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>2018-03-14 19:08</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>NTCO3</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Modificação de Projeções Divulgadas</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>2018-03-15</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>4.3x</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>2019-08-15 18:44</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>OIBR3</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Apresentação 2T19</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>2019-08-16</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>4.3x</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>7.2x</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>-8.8%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06 18:32</t>
+          <t>2018-03-14 19:08</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>LREN3</t>
+          <t>NTCO3</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Projeções</t>
+          <t>Modificação de Projeções Divulgadas</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2018-03-15</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>4.1x</t>
+          <t>4.3x</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>10.4x</t>
+          <t>3.5x</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -2425,81 +2425,81 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>2025-01-09 18:24</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>OIBR3</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Conclusa~o das Negociac¸o~es para alienação da UPI Ativos TV por Assinatura</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>4.1x</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>7.9x</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>+6.3%</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2025-10-30 18:28</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>VIVT3</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação de Resultados 3T25</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>4.3x</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3.2x</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>-6.2%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2023-11-08 19:49</t>
+          <t>2019-08-15 18:44</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>BRAV3</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Dados de Produção - Outubro 2023</t>
+          <t>Apresentação 2T19</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>4.1x</t>
+          <t>4.3x</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>4.3x</t>
+          <t>7.2x</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -2509,39 +2509,39 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.8%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2025-11-13 18:18</t>
+          <t>2026-08-06 18:32</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>HAPV3</t>
+          <t>LREN3</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Programa de Recompra de Ações</t>
+          <t>Projeções</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>4.0x</t>
+          <t>4.1x</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>10.1x</t>
+          <t>10.4x</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -2551,81 +2551,81 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-8.4%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>2024-11-13 18:50</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>LIGT3</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Ratificação das versões finais dos Instrumentos Locais</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>4.0x</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>6.3x</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>-6.3%</t>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>2025-01-09 18:24</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>OIBR3</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Conclusa~o das Negociac¸o~es para alienação da UPI Ativos TV por Assinatura</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>4.1x</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>7.9x</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>+6.3%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2024-03-06 22:45</t>
+          <t>2023-11-08 19:49</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>BRAV3</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Release de ESG 4T23 e 2023</t>
+          <t>Dados de Produção - Outubro 2023</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>4.0x</t>
+          <t>4.1x</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3.2x</t>
+          <t>4.3x</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -2635,29 +2635,29 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-3.9%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2022-02-23 18:42</t>
+          <t>2025-11-05 18:05</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>RDOR3</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Associação Rede D'Or e SulAmérica</t>
+          <t>Recompra e Cancelamento Bond 2031</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>5.8x</t>
+          <t>6.2x</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -2677,81 +2677,81 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-14.5%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2024-08-14 20:06</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>OIBR3</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Apresentação de Resultados 2T24</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>3.9x</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>8.6x</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>+10.2%</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-13 18:18</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>HAPV3</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Programa de Recompra de Ações</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>4.0x</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>10.1x</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>-6.0%</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2024-05-08 18:37</t>
+          <t>2024-11-13 18:50</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>COGN3</t>
+          <t>LIGT3</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Revisão do guidance da Controlada Vasta - Alteração no ACV (Valor Anual do Contrato) de  16% - 18% para 12% no ciclo 2024</t>
+          <t>Ratificação das versões finais dos Instrumentos Locais</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>3.9x</t>
+          <t>4.0x</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>5.2x</t>
+          <t>6.3x</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -2761,165 +2761,165 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.3%</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2022-06-29 17:43</t>
+          <t>2024-03-06 22:45</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>LIGT3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Renúncia de Administrador</t>
+          <t>Release de ESG 4T23 e 2023</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
+          <t>4.0x</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3.2x</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>-4.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>2022-02-23 18:42</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>RDOR3</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Associação Rede D'Or e SulAmérica</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>4.0x</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>5.8x</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>-8.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2024-08-14 20:06</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>OIBR3</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Apresentação de Resultados 2T24</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
           <t>3.9x</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>6.7x</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>-17.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2024-11-05 19:01</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>GOAU4</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Cancelamento de ações em tesouraria</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>3.9x</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>3.8x</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>8.6x</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>+8.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>2018-11-07 19:49</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>YDUQ3</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Apresentação de Resultados 3T18</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>2018-11-08</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>3.8x</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>4.5x</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>-8.8%</t>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>+10.2%</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2024-11-06 21:45</t>
+          <t>2024-05-08 18:37</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>OIBR3</t>
+          <t>COGN3</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Apresentação de Resultados 3T24</t>
+          <t>Revisão do guidance da Controlada Vasta - Alteração no ACV (Valor Anual do Contrato) de  16% - 18% para 12% no ciclo 2024</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>3.8x</t>
+          <t>3.9x</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>1.9x</t>
+          <t>5.2x</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -2929,83 +2929,83 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-5.8%</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>2025-08-04 19:35</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>BBSE3</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Modificação de Projeções Divulgadas</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>3.8x</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>1.3x</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>+1.1%</t>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>2022-06-29 17:43</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>LIGT3</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Renúncia de Administrador</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>3.9x</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>6.7x</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>-17.0%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2020-03-10 22:00</t>
+          <t>2024-11-05 19:01</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>OIBR3</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Proposta pela Móvel</t>
+          <t>Cancelamento de ações em tesouraria</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
+          <t>3.9x</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
           <t>3.8x</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>3.9x</t>
-        </is>
-      </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
@@ -3013,291 +3013,291 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>+4.4%</t>
+          <t>+8.8%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t>2018-11-07 19:49</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>YDUQ3</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação de Resultados 3T18</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>4.5x</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>-8.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>2024-11-06 21:45</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>OIBR3</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação de Resultados 3T24</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>1.9x</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>2020-03-10 22:00</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>OIBR3</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Proposta pela Móvel</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>3.9x</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>+4.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
           <t>2024-03-08 20:16</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Petrobras esclarece notícia divulgada na mídia</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>2024-03-11</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>3.8x</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>3.6x</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>CAIU</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>-2.9%</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>2021-04-16 18:28</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Petrobras sobre renúncia de Conselheiro de Administração</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>2021-04-19</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>3.7x</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>3.2x</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>+5.6%</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>2026-08-06 17:52</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>ASAI3</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Eleição do Sr. Rafael Sachete da Silva para o cargo de Diretor de Relações com Investidores</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>3.7x</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>2.6x</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>CAIU</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>-3.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>2024-02-27 19:36</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>PSSA3</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Apresentação dos Resultados do 4T23</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>2024-02-28</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>3.7x</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>4.9x</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>+5.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>2025-05-08 22:33</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>CSNA3</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Release ESG 1T25</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>3.6x</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>3.1x</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>-10.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>2025-12-16 23:52</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>BRAV3</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Esclarecimento acerca de notícia divulgada na mídia</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>3.6x</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>3.7x</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>+3.6%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2018-09-24 19:40</t>
+          <t>2024-02-27 19:36</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>BRKM5</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Celebração, Alteração ou Rescisão de Acordo de Acionistas</t>
+          <t>Apresentação dos Resultados do 4T23</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>3.6x</t>
+          <t>3.7x</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>1.2x</t>
+          <t>4.9x</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -3307,29 +3307,29 @@
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>+4.0%</t>
+          <t>+5.8%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2018-04-25 23:00</t>
+          <t>2025-05-08 22:33</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Apresentação de Resultados 1T18</t>
+          <t>Release ESG 1T25</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>3.9x</t>
+          <t>3.1x</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -3349,14 +3349,14 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.4%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2025-03-21 18:46</t>
+          <t>2025-12-16 23:52</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Apresentação Divulgação de Resultados 4T24 &amp;amp 2024</t>
+          <t>Esclarecimento acerca de notícia divulgada na mídia</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>2.6x</t>
+          <t>3.7x</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -3391,71 +3391,71 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>+3.6%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>2020-03-11 17:32</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2018-09-24 19:40</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>BRKM5</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Término da monitoria na Braskem prevista no Acordo de Leniência firmado entre a Companhia e Ministério Público Federal em 14 de dezembro de 2016</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>2020-03-12</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Celebração, Alteração ou Rescisão de Acordo de Acionistas</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>2018-09-25</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>3.6x</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>2.0x</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>-27.6%</t>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>1.2x</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2020-04-23 20:35</t>
+          <t>2018-04-25 23:00</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Rerratificação dos termos e condições da 25ª  emissão de debêntures</t>
+          <t>Apresentação de Resultados 1T18</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>2020-04-24</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>3.9x</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -3475,91 +3475,91 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>2022-11-09 23:53</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>B3SA3</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Aquisição da Neurotech</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>2022-11-10</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>2.7x</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>2025-03-21 18:46</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>BRAV3</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Apresentação Divulgação de Resultados 4T24 &amp;amp 2024</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>3.6x</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>2.6x</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>+9.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>2020-03-11 17:32</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>BRKM5</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Término da monitoria na Braskem prevista no Acordo de Leniência firmado entre a Companhia e Ministério Público Federal em 14 de dezembro de 2016</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>3.6x</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>2.0x</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>CAIU</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>-13.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>2021-11-19 20:28</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>TIMS3</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Próximas Lives Programadas.</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>2021-11-22</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>3.5x</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>5.1x</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>+1.7%</t>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>-27.6%</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1273 comunicados da Petrobras após o fechamento no período</t>
+          <t>1338 comunicados da Petrobras após o fechamento no período</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2025-11-06 19:20</t>
+          <t>2020-06-12 18:29</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Petrobras informa sobre remuneração aos acionistas</t>
+          <t>Petrobras inicia fase vinculante de usinas eólicas</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>2.3x</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>2.7x</t>
+          <t>1.0x</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -4399,98 +4399,98 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>+0.5%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>2020-06-12 18:29</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2021-10-18 21:37</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Petrobras inicia fase vinculante de usinas eólicas</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>2020-06-15</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras esclarece sobre notícias da imprensa</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2021-10-19</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>2.3x</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>1.5x</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>-5.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2020-03-09 18:10</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras assina contrato para venda de campos terrestres</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>2020-03-10</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>2.3x</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>2.1x</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>SUBIU</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>+0.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>2021-10-18 21:37</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Petrobras esclarece sobre notícias da imprensa</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>2.3x</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>1.5x</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>-5.0%</t>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>+9.0%</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2020-03-09 18:10</t>
+          <t>2019-08-20 17:25</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Petrobras assina contrato para venda de campos terrestres</t>
+          <t>Petrobras informa sobre decisão favorável do CARF relacionada à cobrança de CIDE-Importação referente a contratos de afretamento</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2019-08-21</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>2.1x</t>
+          <t>1.7x</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -4525,56 +4525,56 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>+9.0%</t>
+          <t>+5.8%</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>2019-08-20 17:25</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>2023-07-26 18:43</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Petrobras informa sobre decisão favorável do CARF relacionada à cobrança de CIDE-Importação referente a contratos de afretamento</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>2019-08-21</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Relatório de Produção e Vendas 2T23</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>2.3x</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>1.7x</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>+5.8%</t>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>1.9x</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>CAIU</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>-5.3%</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2023-07-26 18:43</t>
+          <t>2022-10-21 18:50</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Relatório de Produção e Vendas 2T23</t>
+          <t>Petrobras sobre venda da rede de fibra óptica onshore</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>1.9x</t>
+          <t>1.5x</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -4609,14 +4609,14 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2022-10-21 18:50</t>
+          <t>2019-03-21 18:18</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -4626,22 +4626,22 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Petrobras sobre venda da rede de fibra óptica onshore</t>
+          <t>Hibernação da fábrica de fertilizantes na Bahia</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2019-03-22</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>2.3x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>1.5x</t>
+          <t>1.6x</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -4651,140 +4651,140 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>2019-03-21 18:18</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-17 20:11</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>PETR4</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Hibernação da fábrica de fertilizantes na Bahia</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>2019-03-22</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>2.2x</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>1.6x</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras recebe pagamento da primeira parcela do Programa de subvenção econômica do diesel</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>2.1x</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>1.2x</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2020-07-13 20:17</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Petrobras sobre venda de asfalto pela Reduc</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>2.1x</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>1.7x</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>SUBIU</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>+3.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>2019-07-15 19:53</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Petrobras divulga início de fase não vinculante para venda de ativos em refino e logística no país</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>2.1x</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>1.4x</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>CAIU</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>-5.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-06 19:19</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Petrobras informa sobre remuneração aos acionistas</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>2.2x</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>3.6x</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>CAIU</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>-3.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>2020-07-13 20:17</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>PETR4</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Petrobras sobre venda de asfalto pela Reduc</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>2.1x</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>1.7x</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>SUBIU</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>+3.3%</t>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>-1.2%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2019-07-15 19:53</t>
+          <t>2022-12-13 20:23</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Petrobras divulga início de fase não vinculante para venda de ativos em refino e logística no país</t>
+          <t>Petrobras sobre o Polo Bahia Terra</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2022-12-14</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>1.4x</t>
+          <t>4.4x</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-8.3%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2022-12-13 20:23</t>
+          <t>2025-04-03 19:43</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Petrobras sobre o Polo Bahia Terra</t>
+          <t>Petrobras arquiva Form 20-F 2024</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>2022-12-14</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>4.4x</t>
+          <t>3.9x</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-4.1%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2025-04-03 19:43</t>
+          <t>2019-12-12 19:20</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -4878,22 +4878,22 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Petrobras arquiva Form 20-F 2024</t>
+          <t>Petrobras sobre melhora da perspectiva de rating global pela S&amp;ampP</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2019-12-13</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>2.1x</t>
+          <t>2.0x</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3.9x</t>
+          <t>2.7x</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
     </row>
